--- a/output/full_scan/batch_seq1_2026-07-20.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-20.xlsx
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>223.7736866641334</v>
+        <v>223.7736866641333</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>12.15</v>
